--- a/output/roomself_excel/6603.xlsx
+++ b/output/roomself_excel/6603.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35908</v>
+        <v>45300</v>
       </c>
       <c r="D2" t="n">
-        <v>1516</v>
+        <v>1808</v>
       </c>
       <c r="E2" t="n">
-        <v>207</v>
+        <v>318</v>
       </c>
       <c r="F2" t="n">
-        <v>204</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50470</v>
+        <v>71272</v>
       </c>
       <c r="D3" t="n">
-        <v>1804</v>
+        <v>2152</v>
       </c>
       <c r="E3" t="n">
-        <v>429</v>
+        <v>236</v>
       </c>
       <c r="F3" t="n">
-        <v>220</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -510,17 +510,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23493</v>
+        <v>192270</v>
       </c>
       <c r="D4" t="n">
-        <v>1256</v>
+        <v>3560</v>
       </c>
       <c r="E4" t="n">
-        <v>123</v>
+        <v>413</v>
       </c>
       <c r="F4" t="n">
         <v>16</v>
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>130054</v>
+        <v>86976</v>
       </c>
       <c r="D5" t="n">
-        <v>3076</v>
+        <v>2360</v>
       </c>
       <c r="E5" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F5" t="n">
-        <v>223</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>126945</v>
+        <v>94622</v>
       </c>
       <c r="D6" t="n">
-        <v>2952</v>
+        <v>2608</v>
       </c>
       <c r="E6" t="n">
-        <v>481</v>
+        <v>319</v>
       </c>
       <c r="F6" t="n">
-        <v>305</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>329724</v>
+        <v>65052</v>
       </c>
       <c r="D7" t="n">
-        <v>7888</v>
+        <v>2048</v>
       </c>
       <c r="E7" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>94622</v>
+        <v>94293</v>
       </c>
       <c r="D8" t="n">
-        <v>2608</v>
+        <v>2600</v>
       </c>
       <c r="E8" t="n">
-        <v>335</v>
+        <v>251</v>
       </c>
       <c r="F8" t="n">
-        <v>186</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -620,17 +620,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23716</v>
+        <v>128175</v>
       </c>
       <c r="D9" t="n">
-        <v>1232</v>
+        <v>2944</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>65052</v>
+        <v>50470</v>
       </c>
       <c r="D10" t="n">
-        <v>2048</v>
+        <v>1804</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10692</v>
+        <v>23716</v>
       </c>
       <c r="D11" t="n">
-        <v>828</v>
+        <v>1232</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12650</v>
+        <v>17400</v>
       </c>
       <c r="D12" t="n">
-        <v>900</v>
+        <v>1064</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12420</v>
+        <v>18618</v>
       </c>
       <c r="D13" t="n">
-        <v>892</v>
+        <v>1124</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -730,17 +730,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17400</v>
+        <v>23493</v>
       </c>
       <c r="D14" t="n">
-        <v>1064</v>
+        <v>1256</v>
       </c>
       <c r="E14" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F14" t="n">
         <v>16</v>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12412</v>
+        <v>12650</v>
       </c>
       <c r="D15" t="n">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>94293</v>
+        <v>12420</v>
       </c>
       <c r="D16" t="n">
-        <v>2600</v>
+        <v>892</v>
       </c>
       <c r="E16" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>128175</v>
+        <v>12412</v>
       </c>
       <c r="D17" t="n">
-        <v>2944</v>
+        <v>892</v>
       </c>
       <c r="E17" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>45300</v>
+        <v>126945</v>
       </c>
       <c r="D18" t="n">
-        <v>1808</v>
+        <v>2952</v>
       </c>
       <c r="E18" t="n">
-        <v>318</v>
+        <v>481</v>
       </c>
       <c r="F18" t="n">
-        <v>166</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>71272</v>
+        <v>35908</v>
       </c>
       <c r="D19" t="n">
-        <v>2152</v>
+        <v>1516</v>
       </c>
       <c r="E19" t="n">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20">
@@ -862,17 +862,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>86976</v>
+        <v>130054</v>
       </c>
       <c r="D20" t="n">
-        <v>2360</v>
+        <v>3076</v>
       </c>
       <c r="E20" t="n">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="F20" t="n">
         <v>16</v>
@@ -884,20 +884,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>18618</v>
+        <v>137454</v>
       </c>
       <c r="D21" t="n">
-        <v>1124</v>
+        <v>4984</v>
       </c>
       <c r="E21" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10692</v>
+      </c>
+      <c r="D22" t="n">
+        <v>828</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/6603.xlsx
+++ b/output/roomself_excel/6603.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>1808</v>
       </c>
-      <c r="E2" t="n">
-        <v>318</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>166</v>
+        <v>302</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>150</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +533,20 @@
       <c r="D3" t="n">
         <v>2152</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>236</v>
       </c>
-      <c r="F3" t="n">
-        <v>16</v>
-      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +563,20 @@
       <c r="D4" t="n">
         <v>3560</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>413</v>
       </c>
-      <c r="F4" t="n">
-        <v>16</v>
-      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +593,20 @@
       <c r="D5" t="n">
         <v>2360</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>288</v>
       </c>
-      <c r="F5" t="n">
-        <v>16</v>
-      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +623,20 @@
       <c r="D6" t="n">
         <v>2608</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>319</v>
       </c>
-      <c r="F6" t="n">
-        <v>16</v>
-      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +653,20 @@
       <c r="D7" t="n">
         <v>2048</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +683,20 @@
       <c r="D8" t="n">
         <v>2600</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>251</v>
       </c>
-      <c r="F8" t="n">
-        <v>16</v>
-      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,10 +713,26 @@
       <c r="D9" t="n">
         <v>2944</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>351</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>385</v>
       </c>
-      <c r="F9" t="n">
+      <c r="J9" t="n">
         <v>16</v>
       </c>
     </row>
@@ -651,11 +751,27 @@
       <c r="D10" t="n">
         <v>1804</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>206</v>
       </c>
-      <c r="F10" t="n">
-        <v>16</v>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>245</v>
+      </c>
+      <c r="J10" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -673,12 +789,20 @@
       <c r="D11" t="n">
         <v>1232</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>82</v>
       </c>
-      <c r="F11" t="n">
-        <v>16</v>
-      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +819,20 @@
       <c r="D12" t="n">
         <v>1064</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>116</v>
       </c>
-      <c r="F12" t="n">
-        <v>16</v>
-      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +849,20 @@
       <c r="D13" t="n">
         <v>1124</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>174</v>
       </c>
-      <c r="F13" t="n">
-        <v>16</v>
-      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +879,20 @@
       <c r="D14" t="n">
         <v>1256</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>123</v>
       </c>
-      <c r="F14" t="n">
-        <v>16</v>
-      </c>
+      <c r="G14" t="n">
+        <v>16</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +909,12 @@
       <c r="D15" t="n">
         <v>900</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +931,20 @@
       <c r="D16" t="n">
         <v>892</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="G16" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +961,12 @@
       <c r="D17" t="n">
         <v>892</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,11 +983,27 @@
       <c r="D18" t="n">
         <v>2952</v>
       </c>
-      <c r="E18" t="n">
-        <v>481</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>305</v>
+        <v>273</v>
+      </c>
+      <c r="G18" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>588</v>
+      </c>
+      <c r="J18" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -849,11 +1021,27 @@
       <c r="D19" t="n">
         <v>1516</v>
       </c>
-      <c r="E19" t="n">
-        <v>207</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>204</v>
+        <v>191</v>
+      </c>
+      <c r="G19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>188</v>
+      </c>
+      <c r="J19" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -871,10 +1059,26 @@
       <c r="D20" t="n">
         <v>3076</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>356</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>274</v>
       </c>
-      <c r="F20" t="n">
+      <c r="J20" t="n">
         <v>16</v>
       </c>
     </row>
@@ -893,12 +1097,12 @@
       <c r="D21" t="n">
         <v>4984</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1119,12 @@
       <c r="D22" t="n">
         <v>828</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
